--- a/uploads/UPLOAD-TEMPLATE/STAFFS-DEPLOY-TEMPLATE.xlsx
+++ b/uploads/UPLOAD-TEMPLATE/STAFFS-DEPLOY-TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSH TEMPLATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6F5D39-A376-4337-84BA-07FA4C3EEAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8434C07B-13D7-4D56-9ECE-F859C81CF926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8DE630E0-0B89-4DDE-A92E-DF514EA9A919}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>* delete this line and above sample data on actual uploading</t>
   </si>
   <si>
-    <t>Store</t>
-  </si>
-  <si>
     <t>End Date</t>
   </si>
   <si>
@@ -49,6 +46,9 @@
   </si>
   <si>
     <t>V211013-000004</t>
+  </si>
+  <si>
+    <t>New Store</t>
   </si>
 </sst>
 </file>
@@ -451,21 +451,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2">
         <v>46230</v>

--- a/uploads/UPLOAD-TEMPLATE/STAFFS-DEPLOY-TEMPLATE.xlsx
+++ b/uploads/UPLOAD-TEMPLATE/STAFFS-DEPLOY-TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSH TEMPLATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8434C07B-13D7-4D56-9ECE-F859C81CF926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A069770-04AA-4958-BA16-E9F91B118EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8DE630E0-0B89-4DDE-A92E-DF514EA9A919}"/>
   </bookViews>
@@ -470,9 +470,7 @@
       <c r="C2" s="2">
         <v>46230</v>
       </c>
-      <c r="D2" s="2">
-        <v>46233</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
